--- a/erp-server/erp-server-file/src/main/resources/excel/wms/afterSalePackExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/afterSalePackExport.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>箱唛</t>
   </si>
@@ -93,6 +93,12 @@
   </si>
   <si>
     <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.operateUserName}</t>
+  </si>
+  <si>
+    <t>{.check_user_name}</t>
   </si>
 </sst>
 </file>
@@ -1366,10 +1372,10 @@
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
